--- a/INSTANCES/instances_xlsx/A_MTN_8/358FL_15A_4.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/358FL_15A_4.xlsx
@@ -11457,7 +11457,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -11474,7 +11474,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -11491,7 +11491,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -11508,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -11542,7 +11542,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -11627,7 +11627,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -11661,7 +11661,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>1</v>
